--- a/AI Planning/Job Scheduling/Job To Machine/problemset/solution/ljf/supermercado-150j-20m-5_20tr-same_per_machined-39c_ljf.xlsx
+++ b/AI Planning/Job Scheduling/Job To Machine/problemset/solution/ljf/supermercado-150j-20m-5_20tr-same_per_machined-39c_ljf.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Compra #SF571</t>
+          <t>Compra #UX090</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rafael Carmona</t>
+          <t>Fernando Daniel</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -479,12 +479,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Compra #FH239</t>
+          <t>Compra #FS673</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rafael Carmona</t>
+          <t>Fernando Daniel</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -500,12 +500,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Compra #HN989</t>
+          <t>Compra #UN066</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rafael Carmona</t>
+          <t>Fernando Daniel</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -521,12 +521,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Compra #SA266</t>
+          <t>Compra #AN636</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rafael Carmona</t>
+          <t>Fernando Daniel</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -542,12 +542,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Compra #SE883</t>
+          <t>Compra #EU242</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rafael Carmona</t>
+          <t>Fernando Daniel</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -563,12 +563,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Compra #HF916</t>
+          <t>Compra #SF493</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rafael Carmona</t>
+          <t>Fernando Daniel</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -584,12 +584,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Compra #FU595</t>
+          <t>Compra #TF107</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rafael Carmona</t>
+          <t>Fernando Daniel</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -605,565 +605,565 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Compra #HT606</t>
+          <t>Compra #HH210</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cristhian Amaya</t>
+          <t>Fabio Ramírez</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Compra #TT594</t>
+          <t>Compra #AS087</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cristhian Amaya</t>
+          <t>Fabio Ramírez</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Compra #SU330</t>
+          <t>Compra #NH970</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cristhian Amaya</t>
+          <t>Fabio Ramírez</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Compra #XU821</t>
+          <t>Compra #AA331</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cristhian Amaya</t>
+          <t>Fabio Ramírez</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Compra #TT159</t>
+          <t>Compra #XA825</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cristhian Amaya</t>
+          <t>Fabio Ramírez</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Compra #UX515</t>
+          <t>Compra #NF899</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cristhian Amaya</t>
+          <t>Fabio Ramírez</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
+        <v>25</v>
+      </c>
+      <c r="E14" t="n">
         <v>30</v>
-      </c>
-      <c r="E14" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Compra #EH349</t>
+          <t>Compra #XN598</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Enrique Orlando</t>
+          <t>Fabio Ramírez</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compra #UT861</t>
+          <t>Compra #TE891</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Enrique Orlando</t>
+          <t>Luis Perdomo</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
         <v>7</v>
-      </c>
-      <c r="E16" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Compra #SN780</t>
+          <t>Compra #HU214</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Enrique Orlando</t>
+          <t>Luis Perdomo</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="n">
         <v>14</v>
-      </c>
-      <c r="E17" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Compra #HT619</t>
+          <t>Compra #AT801</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Enrique Orlando</t>
+          <t>Luis Perdomo</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
+        <v>14</v>
+      </c>
+      <c r="E18" t="n">
         <v>21</v>
-      </c>
-      <c r="E18" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Compra #SA764</t>
+          <t>Compra #UA927</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Enrique Orlando</t>
+          <t>Luis Perdomo</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
+        <v>21</v>
+      </c>
+      <c r="E19" t="n">
         <v>28</v>
-      </c>
-      <c r="E19" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Compra #XN310</t>
+          <t>Compra #AH503</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Consuelo María</t>
+          <t>Luis Perdomo</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compra #XA788</t>
+          <t>Compra #UF491</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Consuelo María</t>
+          <t>Jimmy Mejía</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>8</v>
       </c>
       <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
         <v>8</v>
-      </c>
-      <c r="E21" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Compra #XT510</t>
+          <t>Compra #FT660</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Consuelo María</t>
+          <t>Jimmy Mejía</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>8</v>
       </c>
       <c r="D22" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" t="n">
         <v>16</v>
-      </c>
-      <c r="E22" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Compra #XN403</t>
+          <t>Compra #TU599</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Consuelo María</t>
+          <t>Jimmy Mejía</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>8</v>
       </c>
       <c r="D23" t="n">
+        <v>16</v>
+      </c>
+      <c r="E23" t="n">
         <v>24</v>
-      </c>
-      <c r="E23" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Compra #XT217</t>
+          <t>Compra #NS517</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Catherine Ocampo</t>
+          <t>Jimmy Mejía</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Compra #XT266</t>
+          <t>Compra #SE951</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Catherine Ocampo</t>
+          <t>Jesús Carlos</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>9</v>
       </c>
       <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
         <v>9</v>
-      </c>
-      <c r="E25" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Compra #NE368</t>
+          <t>Compra #AU481</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Catherine Ocampo</t>
+          <t>Jesús Carlos</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>9</v>
       </c>
       <c r="D26" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" t="n">
         <v>18</v>
-      </c>
-      <c r="E26" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Compra #FU161</t>
+          <t>Compra #XX759</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Catherine Ocampo</t>
+          <t>Jesús Carlos</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>9</v>
       </c>
       <c r="D27" t="n">
+        <v>18</v>
+      </c>
+      <c r="E27" t="n">
         <v>27</v>
-      </c>
-      <c r="E27" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Compra #HS294</t>
+          <t>Compra #UA701</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fernando Hernández</t>
+          <t>Jesús Carlos</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E28" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Compra #UX016</t>
+          <t>Compra #NF995</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fernando Hernández</t>
+          <t>Jesús Reyes</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>9</v>
       </c>
       <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
         <v>9</v>
-      </c>
-      <c r="E29" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Compra #SF562</t>
+          <t>Compra #HU961</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fernando Hernández</t>
+          <t>Jesús Reyes</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>9</v>
       </c>
       <c r="D30" t="n">
+        <v>9</v>
+      </c>
+      <c r="E30" t="n">
         <v>18</v>
-      </c>
-      <c r="E30" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Compra #TS454</t>
+          <t>Compra #HF912</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fernando Hernández</t>
+          <t>Jesús Reyes</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>9</v>
       </c>
       <c r="D31" t="n">
+        <v>18</v>
+      </c>
+      <c r="E31" t="n">
         <v>27</v>
-      </c>
-      <c r="E31" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Compra #EU350</t>
+          <t>Compra #FS666</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jesús David</t>
+          <t>Jesús Reyes</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Compra #UA653</t>
+          <t>Compra #XE105</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jesús David</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Compra #UT964</t>
+          <t>Compra #HF409</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jesús David</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D34" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E34" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Compra #EF321</t>
+          <t>Compra #TE060</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jesús David</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D35" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E35" t="n">
         <v>36</v>
@@ -1172,432 +1172,432 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Compra #AF003</t>
+          <t>Compra #HF244</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Javier William</t>
+          <t>Yenny María</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Compra #AS540</t>
+          <t>Compra #UX040</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Javier William</t>
+          <t>Yenny María</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D37" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E37" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Compra #NT528</t>
+          <t>Compra #FS108</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ernesto Mora</t>
+          <t>Yenny María</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E38" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Compra #NH267</t>
+          <t>Compra #AT723</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ernesto Mora</t>
+          <t>Edwin Leandro</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D39" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Compra #NT666</t>
+          <t>Compra #XS934</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Carolina Alejandra</t>
+          <t>Edwin Leandro</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E40" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Compra #AH254</t>
+          <t>Compra #AE532</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Carolina Alejandra</t>
+          <t>Edwin Leandro</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D41" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E41" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Compra #NA812</t>
+          <t>Compra #NU117</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wilmer Alberto</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Compra #AU258</t>
+          <t>Compra #XE857</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wilmer Alberto</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D43" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E43" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Compra #UE879</t>
+          <t>Compra #TU041</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rosa Cárdenas</t>
+          <t>Lilia Ochoa</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Compra #HF595</t>
+          <t>Compra #AN543</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rosa Cárdenas</t>
+          <t>Lilia Ochoa</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D45" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E45" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Compra #SX609</t>
+          <t>Compra #FX224</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Luis Díaz</t>
+          <t>Olga Gil</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Compra #EF196</t>
+          <t>Compra #NA138</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Luis Díaz</t>
+          <t>Olga Gil</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D47" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E47" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Compra #TE731</t>
+          <t>Compra #HN220</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Carmen Suárez</t>
+          <t>Manuel Alberto</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Compra #EA732</t>
+          <t>Compra #UA562</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Carmen Suárez</t>
+          <t>Manuel Alberto</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E49" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Compra #AN010</t>
+          <t>Compra #NS699</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Karen Pineda</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Compra #NE115</t>
+          <t>Compra #HT993</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Karen Pineda</t>
+          <t>María Sánchez</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E51" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Compra #XS657</t>
+          <t>Compra #XU805</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Armando Arteaga</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Compra #TT150</t>
+          <t>Compra #XT218</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Armando Arteaga</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D53" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E53" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Compra #SX246</t>
+          <t>Compra #UF778</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jessica Ospina</t>
+          <t>Humberto Restrepo</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Compra #UA149</t>
+          <t>Compra #XX372</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jessica Ospina</t>
+          <t>Humberto Restrepo</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E55" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Compra #FH597</t>
+          <t>Compra #HE659</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fabián Fernández</t>
+          <t>Alexandra Mena</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1613,12 +1613,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Compra #AX720</t>
+          <t>Compra #FN068</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fabián Fernández</t>
+          <t>Alexandra Mena</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1634,85 +1634,127 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Compra #SS570</t>
+          <t>Compra #SU088</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Elvia Elvira</t>
+          <t>Luz Esperanza</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Compra #AN638</t>
+          <t>Compra #UU720</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Elvia Elvira</t>
+          <t>Luz Esperanza</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D59" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E59" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Compra #UA928</t>
+          <t>Compra #EA392</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fabián Pedraza</t>
+          <t>Ana Elvira</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Compra #FT017</t>
+          <t>Compra #AF400</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fabián Pedraza</t>
+          <t>Ana Elvira</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D61" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E61" t="n">
-        <v>38</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Compra #EU268</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>María Diana</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>18</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Compra #TF963</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>María Diana</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>18</v>
+      </c>
+      <c r="D63" t="n">
+        <v>18</v>
+      </c>
+      <c r="E63" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
